--- a/business_forms/048_electronic_signature_tool_access_form--business_forms.xlsx
+++ b/business_forms/048_electronic_signature_tool_access_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Form Id 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Description 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>form_description_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Form Description</t>
+          <t>Form Description 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>submitted_date</t>
+          <t>submitted_date_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Submitted Date</t>
+          <t>Submitted Date 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Form Id 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
